--- a/Gov-Tracker_결과.xlsx
+++ b/Gov-Tracker_결과.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O85"/>
+  <dimension ref="A1:O122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -450,7 +450,7 @@
     <col width="28" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="45" customWidth="1" min="9" max="9"/>
+    <col width="42" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>RND</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -559,22 +559,22 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2027년 제조AX분야 산업기술RD사업 과제기획을 위한 기술수요조사 추가 공고</t>
+          <t>2028년도 과학수사감정기법연구개발사업 과제발굴을 위한 연구수요조사 안내</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>77040</t>
+          <t>77109</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>마감</t>
+          <t>접수중</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2027년 제조AX분야 산업기술RD사업 과제기획을 위한 기술수요조사 추가 공고</t>
+          <t>2028년도 과학수사감정기법연구개발사업 과제발굴을 위한 연구수요조사 안내</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4,738</t>
+          <t>4,879</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -693,17 +693,17 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>가을철 안전위험 요소, 안전신문고로 신고하세요!</t>
+          <t>불공정은 단호하게, 민생경제는 살뜰히 범정부 추석 명절 합동점검 실시</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>안전개선과</t>
+          <t>지역경제과</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -733,7 +733,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129154</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129464</t>
         </is>
       </c>
     </row>
@@ -750,7 +750,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>RND</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -760,17 +760,17 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>대형차 우회전 사고부터 침수지역 인명 구조까지, 국민 아이디어로 해결한다</t>
+          <t>폐교를 지역의 활력 거점으로, 행안부-교육부 폐교 활용 지원사업 7건 선정</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>재난안전연구개발과</t>
+          <t>공유재산정책과</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -800,7 +800,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129153</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129463</t>
         </is>
       </c>
     </row>
@@ -827,17 +827,17 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>‘국민안전산업펀드 1호’ 펀드 결성 추진</t>
+          <t>행안부, 민원 담당자 교육 ‘정부24’ 안전성 높이고, ‘서류없는 행정’가속화</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>재난안전산업과</t>
+          <t>통합포털정책과</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -867,7 +867,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129151</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129462</t>
         </is>
       </c>
     </row>
@@ -894,17 +894,17 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>제주4·3사건 희생자·유족 추가 신고  길 열린다... 보상금 신청도 3년 연장</t>
+          <t>9월 가뭄 예·경보 발표</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>사회통합지원과</t>
+          <t>기후재난관리과</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129150</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129452</t>
         </is>
       </c>
     </row>
@@ -961,17 +961,17 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>아세안(ASEAN) 재난관리 역량강화과정,  새로운 4년 여정의 첫발을 내딛다</t>
+          <t>어린이 보호구역 교통사고 다발지역 93개소 점검, 위험요인 개선한다</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>기획협력과</t>
+          <t>안전개선과</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1001,7 +1001,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129108</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129447</t>
         </is>
       </c>
     </row>
@@ -1028,17 +1028,17 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>한일, 지방행정 경험 나누며 협력의 길 찾는다 ‘제26회 한일 내정관계자 교류회의’ 개최</t>
+          <t>세계 각지의 이북도민 44명, 그리운 고국 찾는다</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>자치행정과</t>
+          <t>총무과</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129106</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129446</t>
         </is>
       </c>
     </row>
@@ -1095,17 +1095,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>“영업신고와 사업자등록, 한곳에서 한 번에”  8월 31일부터 원스톱 서비스 전국 시행</t>
+          <t>전국 곳곳 봉사로 채우는 한가위... 행안부, ‘추석맞이 자원봉사 집중기간’ 운영</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>과제발굴과</t>
+          <t>민간협력공동체과</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129105</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129444</t>
         </is>
       </c>
     </row>
@@ -1162,17 +1162,17 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>AI 기반 산업안전, 침수·화재 대응까지, 국민 안전 지키는 우수 기술 한자리에</t>
+          <t>공공 누리집에 숨은 불법광고, 국민이 직접 잡는다</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>재난안전산업과</t>
+          <t>공공서비스혁신과</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129104</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129443</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>지역사랑상품권 5개년 법정 기본계획최초 수립, 지역경제 선순환 이끈다</t>
+          <t>“초연결 시대 더 살기 좋은 지역 만들기“ 행안부, 지자체 우수 정보통신서비스 발굴</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>민생경제지원과</t>
+          <t>공공서비스혁신과</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1269,14 +1269,14 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129103</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129442</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>NIPA</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1286,27 +1286,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RND</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>입찰공고</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>“주민의 아이디어로 지역문제 해결”, 행안부, 2026년 주민자치 우수사례 공모</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>주민자치혁신과</t>
+          <t>[조달청 입찰재공고] K-디지털그랜드챔피언십 2026 운영 용역</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1336,14 +1331,14 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129102</t>
+          <t>https://www.nipa.kr/home/2-3/16932</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>국가AI전략위원회</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1358,27 +1353,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>('26. 8. 31.) 국가AI전략위, 하정우 신임 상근부위원장 취임</t>
+          <t>"지역 청년의 꿈, 키운다"... 행안부-KB국민카드, 함께 청년마을 사업 지원</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>국가AI전략위원회</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>aikoreaadmin</t>
+          <t>사회연대경제지원과</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1408,39 +1398,49 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>https://www.aikorea.go.kr/web/board/brdDetail.do?menu_cd=000012&amp;num=902&amp;currentPage=1&amp;searchData=&amp;searchText=</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129417</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>NIPA</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>사업부</t>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>입찰공고</t>
+          <t>사업공고</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>[조달청 긴급입찰공고] 2026년 하반기 ICT 비즈니스 파트너십 운영 용역</t>
+          <t>2026년도 AI 기반 주파수 간섭분석 및 전파예측기술개발 사업 신규지원 대상과제 공고</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>과학기술정보통신부</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1470,184 +1470,183 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>https://www.nipa.kr/home/2-3/16915</t>
+          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=023617&amp;sorgnBsnsCd=S049944</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>TIPA</t>
+          <t>NIPA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>입찰공고</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>[입찰공고] 2026년 AI정밀의료SW 선도기반조성 사업 성과분석 용역</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>https://www.nipa.kr/home/2-3/16930</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>IRIS</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>R&amp;D</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>ETC</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>지원사업공고</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2026년도 스마트제조기술 전문기업 시범지정 공고</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>중소벤처기업부</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>https://www.tipa.or.kr/s040101/view/id/17674</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>KERIS</t>
-        </is>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="C17" s="3" t="inlineStr">
-        <is>
-          <t>ETC</t>
-        </is>
-      </c>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t>입찰공고</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>2026년 AI 사이버공격 대응 플랫폼 구축(2단계)</t>
-        </is>
-      </c>
-      <c r="F17" s="3" t="inlineStr">
-        <is>
-          <t>재무회계부</t>
-        </is>
-      </c>
-      <c r="G17" s="3" t="inlineStr"/>
-      <c r="H17" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
-        </is>
-      </c>
-      <c r="I17" s="3" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t>시스템구축·전환</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr">
-        <is>
-          <t>NetFUNNEL</t>
-        </is>
-      </c>
-      <c r="M17" s="3" t="inlineStr">
-        <is>
-          <t>구축</t>
-        </is>
-      </c>
-      <c r="N17" s="3" t="inlineStr">
-        <is>
-          <t>마감</t>
-        </is>
-      </c>
-      <c r="O17" s="3" t="inlineStr">
-        <is>
-          <t>https://www.keris.or.kr/main/tender/view/selectTenderList.do?mi=1076</t>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>RND</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>사업공고</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2026년도 가속기핵심기술개발사업 신규과제 공모</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>과학기술정보통신부</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=024117&amp;sorgnBsnsCd=S000848</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>사업부</t>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>RND</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>사업공고</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>디지털 행정서비스와 행정 혁신 경험을 필리핀 공무원과 공유한다</t>
+          <t>2026년도 하반기 방송통신정책연구(R&amp;D) 신규지원 대상과제 공고</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>국제교육협력과</t>
+          <t>과학기술정보통신부</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1677,14 +1676,14 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128979</t>
+          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=023817&amp;sorgnBsnsCd=S001625</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>NIPA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1694,27 +1693,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>입찰공고</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>“민간 AI 역량 모아 공공문제 해결한다” 행안부 ‘2026년 AI 분석모델 개발 경진대회’ 개최</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>공공데이터분석관리과</t>
+          <t>[조달청 입찰공고] 2026년 지역 AX 사업 통합 성과보고회 및 워크숍 행사 운영</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1744,14 +1738,14 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128977</t>
+          <t>https://www.nipa.kr/home/2-3/16928</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>NIPA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1761,27 +1755,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>입찰공고</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2026년 행정안전통계연보 발간</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>데이터정보화담당관</t>
+          <t>[입찰공고] 2026년 디지털인프라(SW) 진단 및 개선 사업 성과분석 용역</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -1811,7 +1800,7 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128976</t>
+          <t>https://www.nipa.kr/home/2-3/16926</t>
         </is>
       </c>
     </row>
@@ -1838,12 +1827,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>[입찰공고] 권역별 AI·ICT 해외진출 전략 설명회 행사 운영 용역</t>
+          <t>[조달청 긴급입찰공고] 2026년 실감형 콘텐츠 제작 지원 인프라 도입</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -1873,14 +1862,14 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>https://www.nipa.kr/home/2-3/16913</t>
+          <t>https://www.nipa.kr/home/2-3/16925</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>국가AI전략위원회</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1895,22 +1884,27 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>해남군 지진 대비태세 점검을 위한 전문가 회의 개최</t>
+          <t>('26. 9. 8.) 국가AI전략위 출범 1년, 대한민국 AI 대전환 성과 본격화</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>지진방재관리과</t>
+          <t>국가AI전략위원회</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>aikoreaadmin</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -1940,44 +1934,44 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128967</t>
+          <t>https://www.aikorea.go.kr/web/board/brdDetail.do?menu_cd=000012&amp;num=923&amp;currentPage=1&amp;searchData=&amp;searchText=</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>KERIS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>사업부</t>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>입찰공고</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>재난안전통신망 교육, ‘기관 맞춤형 실전훈련’ 중심으로 바뀐다</t>
+          <t>[2026-사전-033] 2026년 자유학기제 연계 독서교육 프로그램 개발 연구 사전규격 공고</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>재난안전통신망과</t>
+          <t>재무회계부</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-06</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2007,14 +2001,14 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128927</t>
+          <t>https://www.keris.or.kr/main/tender/view/selectTenderList.do?mi=1076</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>국가AI전략위원회</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2024,27 +2018,32 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>RND</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>보도자료</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>생활 속 안전 실천을 기록하는  「2026년 어린이 안전일기 공모전」 개최</t>
+          <t>('26. 9. 1.) 국가AI전략위, 유럽 주요 정책ㆍ노동계 인사들과 ‘사회적 정당성을 갖춘 국가 AI 전략’ 논의</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>안전문화교육과</t>
+          <t>국가AI전략위원회</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>aikoreaadmin</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2074,14 +2073,14 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128946</t>
+          <t>https://www.aikorea.go.kr/web/board/brdDetail.do?menu_cd=000012&amp;num=912&amp;currentPage=1&amp;searchData=&amp;searchText=</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>조달청</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2091,27 +2090,37 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>입찰공고</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>새 학기에도 안심하고 등교하도록, 학교 주변 위해요소 집중 점검</t>
+          <t>2026년 글로벌 OTT 플랫폼 연계형 제작지원(Rakuten Viki) 사업 조련의 여왕 의상 제작 및 운영 용역</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>안전개선과</t>
+          <t>주식회사 스튜디오 봄</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>박근예</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2141,14 +2150,14 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128942</t>
+          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01706792&amp;bidPbancOrd=000</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>조달청</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2163,22 +2172,27 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>입찰공고</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>「고유가 피해지원금」 8월 31일까지 꼭 사용하세요</t>
+          <t>태평양 도서국 대상 AI 활용 해양수산 ODA 사업 타당성 조사</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>재정정책과</t>
+          <t>한국해양수산개발원</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>배재현</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2208,14 +2222,14 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128941</t>
+          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01706797&amp;bidPbancOrd=000</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>조달청</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2225,27 +2239,37 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>입찰공고</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>복잡한 표·그림 대신 고품질 텍스트로 행안부, 인공지능(AI) 친화적 보고서 전면 도입</t>
+          <t>(가칭)부산환경체험교육관 리모델링공사 가연성폐기물처리용역(계속비)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>혁신행정담당관</t>
+          <t>부산광역시교육청</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>이정행</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2270,19 +2294,19 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>마감</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128940</t>
+          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01706801&amp;bidPbancOrd=000</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>조달청</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2292,27 +2316,37 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>입찰공고</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>해남군 소규모 지진 반복 발생에 따라 관계기관 대책회의 개최</t>
+          <t>아파트전담 소포우편물 위탁배달 용역 2차 공고(화성)</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>지진방재관리과</t>
+          <t>과학기술정보통신부 우정사업본부 경인지방우정청</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>고문정</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2342,19 +2376,19 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128951</t>
+          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01706091&amp;bidPbancOrd=000</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>조달청</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>사업부</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2364,22 +2398,32 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>입찰공고</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>집중호우 피해지역, 복구와 함께 폭염 안전까지 촘촘히 챙긴다</t>
+          <t>2027 KOTRA 지방지원본부 공용차량 리스(이동코트라 업무용)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>기후재난관리과</t>
+          <t>대한무역투자진흥공사</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>이은영</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2404,49 +2448,59 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>마감</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128952</t>
+          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01704432&amp;bidPbancOrd=001</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>조달청</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>사업부</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>입찰공고</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>8.15.~18. 호우 피해 특별재난지역 우선 선포</t>
+          <t>신흥고가차도 철거공사 폐기물처리용역</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>복구지원과</t>
+          <t>경기도 부천시</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>오미정</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2471,49 +2525,59 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>마감</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128944</t>
+          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01705576&amp;bidPbancOrd=000</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>행정안전부</t>
+          <t>조달청</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>사업부</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>공지</t>
+          <t>입찰공고</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>8월 호우 대응 「중앙재난안전대책본부」, 「복구대책지원본부」 체제로 전환</t>
+          <t>청동천 개선복구사업 건설폐기물처리용역</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>복구지원과</t>
+          <t>충청남도 부여군</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>최종욱</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2538,19 +2602,19 @@
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>마감</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128932</t>
+          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01706814&amp;bidPbancOrd=000</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NIPA</t>
+          <t>조달청</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2560,7 +2624,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2570,12 +2634,27 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>[조달청 입찰공고] K-디지털그랜드챔피언십 2026 운영 용역</t>
+          <t>한국지식재산보호원 2026년 K-브랜드 정부인증 제도 종합광고홍보협력사업 협력사 선정</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>한국언론진흥재단</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>박의연</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2605,49 +2684,54 @@
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>https://www.nipa.kr/home/2-3/16911</t>
+          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01698498&amp;bidPbancOrd=000</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>조달청</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>사업부</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>RND</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>사업공고</t>
+          <t>입찰공고</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>2026년 4극3특 과학기술혁신지원사업 사업단 운영(중부권)</t>
+          <t>연건용역_다중 면역질환 단일세포 분석 및 공간 전사체 분석을 통한 치료 후보 물질 도출 및 메타 분석 기반 통합 지도화 연구 용역_PA202601346</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>과학기술정보통신부</t>
+          <t>서울대학교산학협력단</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>박예진</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -2677,86 +2761,87 @@
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=023637&amp;sorgnBsnsCd=S051098</t>
+          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01706489&amp;bidPbancOrd=000</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>IRIS</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>RND</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>사업공고</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>2026년 4극3특 과학기술혁신지원사업 사업단 운영(제주)</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>과학기술정보통신부</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=023637&amp;sorgnBsnsCd=S051104</t>
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>조달청</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C34" s="3" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="D34" s="3" t="inlineStr">
+        <is>
+          <t>입찰공고</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="inlineStr">
+        <is>
+          <t>제3회 대구인디도서전 및 출판센터 공동관 구축 운영 용역</t>
+        </is>
+      </c>
+      <c r="F34" s="3" t="inlineStr">
+        <is>
+          <t>재단법인 대구디지털혁신진흥원</t>
+        </is>
+      </c>
+      <c r="G34" s="3" t="inlineStr">
+        <is>
+          <t>박예진</t>
+        </is>
+      </c>
+      <c r="H34" s="3" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="I34" s="3" t="inlineStr"/>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="K34" s="3" t="inlineStr">
+        <is>
+          <t>시스템구축·전환</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t>NetFUNNEL</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>구축</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01706827&amp;bidPbancOrd=000</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>TIPA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2766,32 +2851,27 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>RND</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>사업공고</t>
+          <t>지원사업공고</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>2026년 4극3특 과학기술혁신지원사업 사업단 운영(전북)</t>
+          <t>'26년 중소기업기술정보진흥원 정책만족도 조사 관련 개인정보 제3자 제공사항 알림</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>과학기술정보통신부</t>
+          <t>중소벤처기업부</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -2821,48 +2901,43 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=023637&amp;sorgnBsnsCd=S051103</t>
+          <t>https://www.tipa.or.kr/s040101/view/id/17686</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>사업부</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>RND</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>사업공고</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>2026년 4극3특 과학기술혁신지원사업 사업단 운영(강원)</t>
+          <t>가을철 안전위험 요소, 안전신문고로 신고하세요!</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>과학기술정보통신부</t>
+          <t>안전개선과</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
           <t>2026-08-31</t>
         </is>
       </c>
@@ -2893,48 +2968,43 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=023637&amp;sorgnBsnsCd=S051102</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129154</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>사업부</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>RND</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>사업공고</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>2026년 4극3특 과학기술혁신지원사업 사업단 운영(동남권)</t>
+          <t>대형차 우회전 사고부터 침수지역 인명 구조까지, 국민 아이디어로 해결한다</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>과학기술정보통신부</t>
+          <t>재난안전연구개발과</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
           <t>2026-08-31</t>
         </is>
       </c>
@@ -2965,48 +3035,43 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=023637&amp;sorgnBsnsCd=S051101</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129153</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>사업부</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>RND</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>사업공고</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>2026년 4극3특 과학기술혁신지원사업 사업단 운영(대경권)</t>
+          <t>‘국민안전산업펀드 1호’ 펀드 결성 추진</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>과학기술정보통신부</t>
+          <t>재난안전산업과</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
           <t>2026-08-31</t>
         </is>
       </c>
@@ -3037,48 +3102,43 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=023637&amp;sorgnBsnsCd=S051100</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129151</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>사업부</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>RND</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>사업공고</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>2026년 4극3특 과학기술혁신지원사업 사업단 운영(호남권)</t>
+          <t>제주4·3사건 희생자·유족 추가 신고  길 열린다... 보상금 신청도 3년 연장</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>과학기술정보통신부</t>
+          <t>사회통합지원과</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
           <t>2026-08-31</t>
         </is>
       </c>
@@ -3109,14 +3169,14 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=023637&amp;sorgnBsnsCd=S051099</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129150</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NIPA</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -3126,22 +3186,27 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>입찰공고</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>[입찰공고] 정보통신산업진흥원 2027~2030년도 주거래은행 선정</t>
+          <t>아세안(ASEAN) 재난관리 역량강화과정,  새로운 4년 여정의 첫발을 내딛다</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>기획협력과</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3171,49 +3236,44 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>https://www.nipa.kr/home/2-3/16906</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129108</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>사업부</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>RND</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>사업공고</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>(일반형, 26-2차) 스케일업 팁스 R&amp;D 지원계획 공고</t>
+          <t>한일, 지방행정 경험 나누며 협력의 길 찾는다 ‘제26회 한일 내정관계자 교류회의’ 개최</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>중소벤처기업부</t>
+          <t>자치행정과</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3238,54 +3298,49 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>마감</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=019614&amp;sorgnBsnsCd=S051564</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129106</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>사업부</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>RND</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>사업공고</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>(일반형, 26-2차) 글로벌 팁스 R&amp;D 지원계획 공고</t>
+          <t>“영업신고와 사업자등록, 한곳에서 한 번에”  8월 31일부터 원스톱 서비스 전국 시행</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>중소벤처기업부</t>
+          <t>과제발굴과</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>2026-08-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3310,24 +3365,24 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>마감</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=020654&amp;sorgnBsnsCd=S051565</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129105</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TIPA</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>사업부</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3337,22 +3392,22 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>지원사업공고</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>2026년 지방소멸대응 유공 포상 후보자 모집 공고</t>
+          <t>AI 기반 산업안전, 침수·화재 대응까지, 국민 안전 지키는 우수 기술 한자리에</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>중소벤처기업부</t>
+          <t>재난안전산업과</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3382,14 +3437,14 @@
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>https://www.tipa.or.kr/s040101/view/id/17623</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129104</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NIPA</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3399,22 +3454,27 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>입찰공고</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>[입찰공고] 	AI ICT 기업 글로벌 진출 지원전략 수립 연구</t>
+          <t>지역사랑상품권 5개년 법정 기본계획최초 수립, 지역경제 선순환 이끈다</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>민생경제지원과</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -3444,14 +3504,14 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>https://www.nipa.kr/home/2-3/16896</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129103</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>NIPA</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3461,22 +3521,27 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>RND</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>입찰공고</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>[조달청 입찰공고] AX 디바이스 도입 확산을 위한 AX 디바이스 수요 발굴 및 분석 용역</t>
+          <t>“주민의 아이디어로 지역문제 해결”, 행안부, 2026년 주민자치 우수사례 공모</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>주민자치혁신과</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -3506,79 +3571,86 @@
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>https://www.nipa.kr/home/2-3/16894</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=129102</t>
         </is>
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
-        <is>
-          <t>NIPA</t>
-        </is>
-      </c>
-      <c r="B46" s="3" t="inlineStr">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>국가AI전략위원회</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
         <is>
           <t>사업부</t>
         </is>
       </c>
-      <c r="C46" s="3" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="D46" s="3" t="inlineStr">
-        <is>
-          <t>입찰공고</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>[입찰공고] K-Health 국민의료 AI서비스 및 산업생태계 구축 사업 성과분석 및 확산 방안 연구 용역</t>
-        </is>
-      </c>
-      <c r="F46" s="3" t="inlineStr"/>
-      <c r="G46" s="3" t="inlineStr"/>
-      <c r="H46" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-04</t>
-        </is>
-      </c>
-      <c r="I46" s="3" t="inlineStr"/>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t>시스템구축·전환</t>
-        </is>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t>NetFUNNEL</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t>구축</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t>https://www.nipa.kr/home/2-3/16891</t>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ETC</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>('26. 8. 31.) 국가AI전략위, 하정우 신임 상근부위원장 취임</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>국가AI전략위원회</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>aikoreaadmin</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>https://www.aikorea.go.kr/web/board/brdDetail.do?menu_cd=000012&amp;num=902&amp;currentPage=1&amp;searchData=&amp;searchText=</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TIPA</t>
+          <t>NIPA</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3593,22 +3665,17 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>지원사업공고</t>
+          <t>입찰공고</t>
         </is>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>「2026년 구매연계ㆍ상생협력 R&amp;D사업 우수성과 유공」 포상 대상자 모집 공고</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>중소벤처기업부</t>
+          <t>[입찰공고] 2026년 2차 누리꿈스퀘어 운영자금 차입 금융기관 선정</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -3638,7 +3705,7 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>https://www.tipa.or.kr/s040101/view/id/17600</t>
+          <t>https://www.nipa.kr/home/2-3/16917</t>
         </is>
       </c>
     </row>
@@ -3655,7 +3722,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>RND</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3665,22 +3732,22 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>2026년도 임무수요기반 성층권 드론 실증 플랫폼 개발 사업 2단계 신규과제 공고</t>
+          <t>2026년도 한-EU 공동연구지원사업 신규과제 공모</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>우주항공청</t>
+          <t>과학기술정보통신부</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -3710,14 +3777,14 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=022957&amp;sorgnBsnsCd=S051446</t>
+          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=023777&amp;sorgnBsnsCd=S002080</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>조달청</t>
+          <t>TIPA</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3732,32 +3799,22 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>입찰공고</t>
+          <t>지원사업공고</t>
         </is>
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>2026학년도 남성초등학교 운반위탁급식(벌크식) 납품업체 선정 입찰</t>
+          <t>「2026년 구매연계ㆍ상생협력 R&amp;D사업 우수성과 유공」 포상 대상자 모집 연장 공고</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>부산광역시교육청 부산광역시서부교육청 남성초등학교</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>하성준</t>
+          <t>중소벤처기업부</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
@@ -3782,19 +3839,19 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>마감</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01660843&amp;bidPbancOrd=000</t>
+          <t>https://www.tipa.or.kr/s040101/view/id/17683</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>조달청</t>
+          <t>NIPA</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3814,27 +3871,12 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>2026년 문화체육관광 연구개발사업 성과조사 분석 및 사업평가 대응 위탁용역</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>한국콘텐츠진흥원</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>박종윤</t>
+          <t>[조달청 긴급입찰공고] 2026년 하반기 ICT 비즈니스 파트너십 운영 용역</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>2026-08-13</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -3859,54 +3901,54 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>마감</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01661573&amp;bidPbancOrd=000</t>
+          <t>https://www.nipa.kr/home/2-3/16915</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>조달청</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>사업부</t>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>입찰공고</t>
+          <t>사업공고</t>
         </is>
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>2026 포항 해병대 문화축제 행사대행 용역</t>
+          <t>(2026-DCP-18_인공지능_딥테크 챌린지 프로젝트(DCP*))</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>경상북도 포항시</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>고성철</t>
+          <t>중소벤처기업부</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-28</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -3936,54 +3978,44 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01661602&amp;bidPbancOrd=000</t>
+          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=019508&amp;sorgnBsnsCd=S051456</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>조달청</t>
+          <t>TIPA</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>사업부</t>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>입찰공고</t>
+          <t>지원사업공고</t>
         </is>
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>2026 국가유산 미디어아트 구 군산세관본관 등 물품임차 용역</t>
+          <t>2026년도 스마트제조기술 전문기업 시범지정 공고</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>전북특별자치도 군산시</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>양미진</t>
+          <t>중소벤처기업부</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4008,19 +4040,19 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>마감</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01661619&amp;bidPbancOrd=000</t>
+          <t>https://www.tipa.or.kr/s040101/view/id/17674</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>조달청</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -4030,32 +4062,27 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>입찰공고</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>2026년 이웃종교스테이 기획 및 행사운영 용역</t>
+          <t>디지털 행정서비스와 행정 혁신 경험을 필리핀 공무원과 공유한다</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>한국종교인평화회의</t>
+          <t>국제교육협력과</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4080,19 +4107,19 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>마감</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01661461&amp;bidPbancOrd=000</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128979</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>조달청</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4102,37 +4129,27 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>입찰공고</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>2026년 제19회 김포 세계인 큰잔치 행사 대행 용역</t>
+          <t>“민간 AI 역량 모아 공공문제 해결한다” 행안부 ‘2026년 AI 분석모델 개발 경진대회’ 개최</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>김포시외국인주민지원센터</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>황유선</t>
+          <t>공공데이터분석관리과</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4157,19 +4174,19 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>마감</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01661458&amp;bidPbancOrd=000</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128977</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>조달청</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4179,37 +4196,27 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>입찰공고</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>2026학년도 상봉중학교  2학년 수련활동 위탁용역 입찰공고(2단계입찰규격-가격분리 동시입찰)</t>
+          <t>2026년 행정안전통계연보 발간</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>서울특별시동부교육청 상봉중학교</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>장현우</t>
+          <t>데이터정보화담당관</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4234,19 +4241,19 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>마감</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01661465&amp;bidPbancOrd=000</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128976</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>조달청</t>
+          <t>NIPA</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4266,27 +4273,12 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>2026학년도 선덕고등학교 1,2학년 소규모테마형 교육여행 위탁용역 업체 선정 전자입찰 공고(긴급)</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>서울특별시교육청 선덕고등학교</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>임현진</t>
+          <t>[입찰공고] 권역별 AI·ICT 해외진출 전략 설명회 행사 운영 용역</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4311,136 +4303,121 @@
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>마감</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01661472&amp;bidPbancOrd=000</t>
+          <t>https://www.nipa.kr/home/2-3/16913</t>
         </is>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
-        <is>
-          <t>조달청</t>
-        </is>
-      </c>
-      <c r="B57" s="3" t="inlineStr">
-        <is>
-          <t>사업부</t>
-        </is>
-      </c>
-      <c r="C57" s="3" t="inlineStr">
-        <is>
-          <t>BID</t>
-        </is>
-      </c>
-      <c r="D57" s="3" t="inlineStr">
-        <is>
-          <t>입찰공고</t>
-        </is>
-      </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>2026년 스마트생태공장 구축사업_컨설팅 용역</t>
-        </is>
-      </c>
-      <c r="F57" s="3" t="inlineStr">
-        <is>
-          <t>(주)삼정산업</t>
-        </is>
-      </c>
-      <c r="G57" s="3" t="inlineStr">
-        <is>
-          <t>박제현</t>
-        </is>
-      </c>
-      <c r="H57" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="I57" s="3" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="K57" s="3" t="inlineStr">
-        <is>
-          <t>시스템구축·전환</t>
-        </is>
-      </c>
-      <c r="L57" s="3" t="inlineStr">
-        <is>
-          <t>NetFUNNEL</t>
-        </is>
-      </c>
-      <c r="M57" s="3" t="inlineStr">
-        <is>
-          <t>구축</t>
-        </is>
-      </c>
-      <c r="N57" s="3" t="inlineStr">
-        <is>
-          <t>마감</t>
-        </is>
-      </c>
-      <c r="O57" s="3" t="inlineStr">
-        <is>
-          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01661481&amp;bidPbancOrd=000</t>
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>IRIS</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>RND</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>사업공고</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>2026년도 2차 신재생에너지R&amp;D(수소) 신규지원대상 연구개발과제 재공고</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>기후에너지환경부</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=023597&amp;sorgnBsnsCd=S002293</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>조달청</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>미분류</t>
+          <t>사업부</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>입찰공고</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>2026학년도 상봉중학교  2학년 수련활동 위탁용역 입찰공고(2단계입찰규격-가격분리 동시입찰)</t>
+          <t>해남군 지진 대비태세 점검을 위한 전문가 회의 개최</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>서울특별시동부교육청 상봉중학교</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>장현우</t>
+          <t>지진방재관리과</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>2026-08-12</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4465,54 +4442,49 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>마감</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01661465&amp;bidPbancOrd=001</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128967</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>IRIS</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>사업부</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>RND</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>사업공고</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>2026년 NCP 활동지원사업 신규과제 2차공모</t>
+          <t>재난안전통신망 교육, ‘기관 맞춤형 실전훈련’ 중심으로 바뀐다</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>과학기술정보통신부</t>
+          <t>재난안전통신망과</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>2026-08-26</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4537,19 +4509,19 @@
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>마감</t>
+          <t>진행중</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=023157&amp;sorgnBsnsCd=S049489</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128927</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>NIPA</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4559,22 +4531,27 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>RND</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>입찰공고</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>[입찰공고] 2026년 평가위원 전문분야 분류체계 개편 방안 조사·분석 용역</t>
+          <t>생활 속 안전 실천을 기록하는  「2026년 어린이 안전일기 공모전」 개최</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>안전문화교육과</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -4604,14 +4581,14 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>https://www.nipa.kr/home/2-3/16881</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128946</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>NIPA</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4621,22 +4598,27 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>입찰공고</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>[입찰공고] 2026년 공공AX 프로젝트 사업 성과분석 용역</t>
+          <t>새 학기에도 안심하고 등교하도록, 학교 주변 위해요소 집중 점검</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>안전개선과</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -4666,14 +4648,14 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>https://www.nipa.kr/home/2-3/16880</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128942</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>NIPA</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4683,22 +4665,27 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>입찰공고</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>[입찰공고] 2026년 부처협업 기반 AI확산 사업 성과분석 용역</t>
+          <t>「고유가 피해지원금」 8월 31일까지 꼭 사용하세요</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>재정정책과</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -4728,44 +4715,44 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>https://www.nipa.kr/home/2-3/16879</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128941</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>TIPA</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>사업부</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>RND</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>지원사업공고</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>2026년 중소기업 R&amp;D 우수성과 50선 모집 연장 공고</t>
+          <t>복잡한 표·그림 대신 고품질 텍스트로 행안부, 인공지능(AI) 친화적 보고서 전면 도입</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>중소벤처기업부</t>
+          <t>혁신행정담당관</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -4795,14 +4782,14 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>https://www.tipa.or.kr/s040101/view/id/17581</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128940</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>NIPA</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4812,22 +4799,27 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>BID</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>입찰공고</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>[조달청 입찰공고] 2026년 클라우드 인식확산 용역</t>
+          <t>해남군 소규모 지진 반복 발생에 따라 관계기관 대책회의 개최</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>지진방재관리과</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -4857,19 +4849,19 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>https://www.nipa.kr/home/2-3/16867</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128951</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>국가AI전략위원회</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>사업부</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -4879,27 +4871,22 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>('26. 7. 22.) 지역·필수·공공의료 공백 해소 위한보건의료 AI 대전환</t>
+          <t>집중호우 피해지역, 복구와 함께 폭염 안전까지 촘촘히 챙긴다</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>국가AI전략위원회</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>aikoreaadmin</t>
+          <t>기후재난관리과</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-08-22</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -4929,117 +4916,111 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>https://www.aikorea.go.kr/web/board/brdDetail.do?menu_cd=000012&amp;num=812&amp;currentPage=1&amp;searchData=&amp;searchText=</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128952</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
-        <is>
-          <t>국가AI전략위원회</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>사업부</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>행정안전부</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>미분류</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
         <is>
           <t>ETC</t>
         </is>
       </c>
-      <c r="D66" s="3" t="inlineStr">
-        <is>
-          <t>보도자료</t>
-        </is>
-      </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>('26. 7. 20.) 국가AI전략위, 「에이전틱 AI 시대 국가 AI 컴퓨팅 전략」 세미나 개최</t>
-        </is>
-      </c>
-      <c r="F66" s="3" t="inlineStr">
-        <is>
-          <t>국가AI전략위원회</t>
-        </is>
-      </c>
-      <c r="G66" s="3" t="inlineStr">
-        <is>
-          <t>aikoreaadmin</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="I66" s="3" t="inlineStr"/>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>상</t>
-        </is>
-      </c>
-      <c r="K66" s="3" t="inlineStr">
-        <is>
-          <t>시스템구축·전환</t>
-        </is>
-      </c>
-      <c r="L66" s="3" t="inlineStr">
-        <is>
-          <t>NetFUNNEL</t>
-        </is>
-      </c>
-      <c r="M66" s="3" t="inlineStr">
-        <is>
-          <t>구축</t>
-        </is>
-      </c>
-      <c r="N66" s="3" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="O66" s="3" t="inlineStr">
-        <is>
-          <t>https://www.aikorea.go.kr/web/board/brdDetail.do?menu_cd=000012&amp;num=801&amp;currentPage=1&amp;searchData=&amp;searchText=</t>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>공지</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>8.15.~18. 호우 피해 특별재난지역 우선 선포</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>복구지원과</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128944</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>TIPA</t>
+          <t>행정안전부</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>미분류</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>RND</t>
+          <t>ETC</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>지원사업공고</t>
+          <t>공지</t>
         </is>
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>제2회 제조AI 솔루션 공모전 공고</t>
+          <t>8월 호우 대응 「중앙재난안전대책본부」, 「복구대책지원본부」 체제로 전환</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>중소벤처기업부</t>
+          <t>복구지원과</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5069,7 +5050,7 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>https://www.tipa.or.kr/s040101/view/id/17570</t>
+          <t>https://www.mois.go.kr/frt/bbs/type010/commonSelectBoardArticle.do?bbsId=BBSMSTR_000000000008&amp;nttId=128932</t>
         </is>
       </c>
     </row>
@@ -5096,12 +5077,12 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>[입찰재공고] 2026 오픈소스 페스티벌 운영 용역</t>
+          <t>[조달청 입찰공고] K-디지털그랜드챔피언십 2026 운영 용역</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5131,14 +5112,14 @@
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>https://www.nipa.kr/home/2-3/16856</t>
+          <t>https://www.nipa.kr/home/2-3/16911</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>KIAT</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5153,27 +5134,27 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>과제</t>
+          <t>사업공고</t>
         </is>
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>2026년 첨단분야 인턴십 지원사업 3차 공고</t>
+          <t>2026년 4극3특 과학기술혁신지원사업 사업단 운영(중부권)</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>산업통상부</t>
+          <t>과학기술정보통신부</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -5203,49 +5184,49 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>https://k-pass.kr/notice/ancList.do</t>
+          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=023637&amp;sorgnBsnsCd=S051098</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>국가AI전략위원회</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>사업부</t>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>RND</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>사업공고</t>
         </is>
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>('26. 7. 14.) 국가AI전략위, ‘AI 데이터센터 산업생태계 육성 간담회’ 개최</t>
+          <t>2026년 4극3특 과학기술혁신지원사업 사업단 운영(제주)</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>국가AI전략위원회</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>aikoreaadmin</t>
+          <t>과학기술정보통신부</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -5270,54 +5251,54 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>마감</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>https://www.aikorea.go.kr/web/board/brdDetail.do?menu_cd=000012&amp;num=791&amp;currentPage=1&amp;searchData=&amp;searchText=</t>
+          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=023637&amp;sorgnBsnsCd=S051104</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>국가AI전략위원회</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>사업부</t>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>RND</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>사업공고</t>
         </is>
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>('26.7.20) Agentic AI 시대 국가 컴퓨팅 전략 세미나</t>
+          <t>2026년 4극3특 과학기술혁신지원사업 사업단 운영(전북)</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>국가AI전략위원회</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>aikorea</t>
+          <t>과학기술정보통신부</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -5342,54 +5323,54 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>마감</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>https://www.aikorea.go.kr/web/board/brdDetail.do?menu_cd=000010&amp;num=787&amp;currentPage=1&amp;searchData=&amp;searchText=</t>
+          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=023637&amp;sorgnBsnsCd=S051103</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>국가AI전략위원회</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>사업부</t>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>RND</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>사업공고</t>
         </is>
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>('26. 7. 8.) 국가AI전략위, ‘AI 시대의 데이터 가치평가’ 세미나 개최</t>
+          <t>2026년 4극3특 과학기술혁신지원사업 사업단 운영(강원)</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>국가AI전략위원회</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>aikoreaadmin</t>
+          <t>과학기술정보통신부</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5414,12 +5395,12 @@
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>마감</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>https://www.aikorea.go.kr/web/board/brdDetail.do?menu_cd=000012&amp;num=782&amp;currentPage=1&amp;searchData=&amp;searchText=</t>
+          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=023637&amp;sorgnBsnsCd=S051102</t>
         </is>
       </c>
     </row>
@@ -5446,7 +5427,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>2026년도 국제공동연구 신속지원사업(미국 제네시스 미션과의 협력을 위한 탐색연구) 신규과제 공모</t>
+          <t>2026년 4극3특 과학기술혁신지원사업 사업단 운영(동남권)</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5456,7 +5437,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -5486,54 +5467,54 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>마감</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=023018&amp;sorgnBsnsCd=S050518</t>
+          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=023637&amp;sorgnBsnsCd=S051101</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>국가AI전략위원회</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>사업부</t>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>RND</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>사업공고</t>
         </is>
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>('26. 7. 7.) 국가AI전략위, 피지컬 AI가 이끄는 자율주행 혁신 간담회 개최</t>
+          <t>2026년 4극3특 과학기술혁신지원사업 사업단 운영(대경권)</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>국가AI전략위원회</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>aikoreaadmin</t>
+          <t>과학기술정보통신부</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5558,19 +5539,19 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>마감</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>https://www.aikorea.go.kr/web/board/brdDetail.do?menu_cd=000012&amp;num=776&amp;currentPage=1&amp;searchData=&amp;searchText=</t>
+          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=023637&amp;sorgnBsnsCd=S051100</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TIPA</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5585,22 +5566,27 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>지원사업공고</t>
+          <t>사업공고</t>
         </is>
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>「2026 스마트공장 지원사업 우수사례 컨소시엄 선정」 참가기업 모집 공고</t>
+          <t>2026년 4극3특 과학기술혁신지원사업 사업단 운영(호남권)</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>중소벤처기업부</t>
+          <t>과학기술정보통신부</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -5625,49 +5611,44 @@
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>마감</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>https://www.tipa.or.kr/s040101/view/id/17537</t>
+          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=023637&amp;sorgnBsnsCd=S051099</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>TIPA</t>
+          <t>NIPA</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>R&amp;D</t>
+          <t>사업부</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>RND</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>지원사업공고</t>
+          <t>입찰공고</t>
         </is>
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>2026년 중소기업 R&amp;D 우수성과 50선 모집 공고</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>중소벤처기업부</t>
+          <t>[입찰공고] 정보통신산업진흥원 2027~2030년도 주거래은행 선정</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -5697,14 +5678,14 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>https://www.tipa.or.kr/s040101/view/id/17524</t>
+          <t>https://www.nipa.kr/home/2-3/16906</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>TIPA</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5714,27 +5695,32 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>RND</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>지원사업공고</t>
+          <t>사업공고</t>
         </is>
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>ICT융합 스마트공장 보급·확산사업 사업비 정산 제2기 스마트 제조혁신 지정회계기관 모집 공고</t>
+          <t>2026년도 NRF 인터내셔널 모빌리티 신규과제 공모</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>중소벤처기업부</t>
+          <t>과학기술정보통신부</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -5764,14 +5750,14 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>https://www.tipa.or.kr/s040101/view/id/17511</t>
+          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=023557&amp;sorgnBsnsCd=S049207</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>TIPA</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5786,12 +5772,12 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>지원사업공고</t>
+          <t>사업공고</t>
         </is>
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>한-호주 글로벌 R&amp;D 협력 포럼 개최 안내</t>
+          <t>(일반형, 26-2차) 스케일업 팁스 R&amp;D 지원계획 공고</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5801,7 +5787,12 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>2026-06-19</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5826,54 +5817,54 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>마감</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>https://www.tipa.or.kr/s040101/view/id/17492</t>
+          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=019614&amp;sorgnBsnsCd=S051564</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>국가AI전략위원회</t>
+          <t>IRIS</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>사업부</t>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>RND</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>사업공고</t>
         </is>
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>('26. 6. 18.) 국가AI전략위, ‘보안취약점 상시 신고조치제 제도화 논의’ 세미나 개최</t>
+          <t>(일반형, 26-2차) 글로벌 팁스 R&amp;D 지원계획 공고</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>국가AI전략위원회</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>aikoreaadmin</t>
+          <t>중소벤처기업부</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -5898,24 +5889,24 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>진행중</t>
+          <t>마감</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>https://www.aikorea.go.kr/web/board/brdDetail.do?menu_cd=000012&amp;num=737&amp;currentPage=1&amp;searchData=&amp;searchText=</t>
+          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=020654&amp;sorgnBsnsCd=S051565</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>국가AI전략위원회</t>
+          <t>TIPA</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>사업부</t>
+          <t>R&amp;D</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -5925,27 +5916,22 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>보도자료</t>
+          <t>지원사업공고</t>
         </is>
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>('26. 6. 17.) 국가AI전략위, 인문사회 기반 AI 융합인재양성 방향 논의</t>
+          <t>2026년 지방소멸대응 유공 포상 후보자 모집 공고</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>국가AI전략위원회</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>aikoreaadmin</t>
+          <t>중소벤처기업부</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -5975,14 +5961,14 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>https://www.aikorea.go.kr/web/board/brdDetail.do?menu_cd=000012&amp;num=733&amp;currentPage=1&amp;searchData=&amp;searchText=</t>
+          <t>https://www.tipa.or.kr/s040101/view/id/17623</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>국가AI전략위원회</t>
+          <t>NIPA</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -5992,32 +5978,22 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>입찰공고</t>
         </is>
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>('26.6.18.) 보안취약점 상시 신고조치제 제도화 관련 세미나</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>국가AI전략위원회</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>aikorea</t>
+          <t>[입찰공고] 	AI ICT 기업 글로벌 진출 지원전략 수립 연구</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -6047,14 +6023,14 @@
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>https://www.aikorea.go.kr/web/board/brdDetail.do?menu_cd=000010&amp;num=731&amp;currentPage=1&amp;searchData=&amp;searchText=</t>
+          <t>https://www.nipa.kr/home/2-3/16896</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>국가AI전략위원회</t>
+          <t>NIPA</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6064,32 +6040,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>ETC</t>
+          <t>BID</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>공지사항</t>
+          <t>입찰공고</t>
         </is>
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>('26.6.17.) AI교육정책 포럼_인문사회 AX 교육은 왜 필요하며 어떻게 할 것인가?</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>국가AI전략위원회</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>aikorea</t>
+          <t>[조달청 입찰공고] AX 디바이스 도입 확산을 위한 AX 디바이스 수요 발굴 및 분석 용역</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -6119,74 +6085,72 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>https://www.aikorea.go.kr/web/board/brdDetail.do?menu_cd=000010&amp;num=729&amp;currentPage=1&amp;searchData=&amp;searchText=</t>
+          <t>https://www.nipa.kr/home/2-3/16894</t>
         </is>
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>TIPA</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>R&amp;D</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>RND</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>지원사업공고</t>
-        </is>
-      </c>
-      <c r="E83" s="2" t="inlineStr">
-        <is>
-          <t>2026년 창업성장기술개발(디딤돌) 소상공인R&amp;D 오디션 시민참여단 모집 안내</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>중소벤처기업부</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>2026-06-05</t>
-        </is>
-      </c>
-      <c r="J83" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="K83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N83" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="O83" t="inlineStr">
-        <is>
-          <t>https://www.tipa.or.kr/s040101/view/id/17459</t>
+      <c r="A83" s="3" t="inlineStr">
+        <is>
+          <t>NIPA</t>
+        </is>
+      </c>
+      <c r="B83" s="3" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C83" s="3" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="D83" s="3" t="inlineStr">
+        <is>
+          <t>입찰공고</t>
+        </is>
+      </c>
+      <c r="E83" s="4" t="inlineStr">
+        <is>
+          <t>[입찰공고] K-Health 국민의료 AI서비스 및 산업생태계 구축 사업 성과분석 및 확산 방안 연구 용역</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="inlineStr"/>
+      <c r="G83" s="3" t="inlineStr"/>
+      <c r="H83" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-04</t>
+        </is>
+      </c>
+      <c r="I83" s="3" t="inlineStr"/>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="K83" s="3" t="inlineStr">
+        <is>
+          <t>시스템구축·전환</t>
+        </is>
+      </c>
+      <c r="L83" s="3" t="inlineStr">
+        <is>
+          <t>NetFUNNEL</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>구축</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O83" s="3" t="inlineStr">
+        <is>
+          <t>https://www.nipa.kr/home/2-3/16891</t>
         </is>
       </c>
     </row>
@@ -6213,7 +6177,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>2026 민관공동기술사업화R&amp;D(구매연계 혁신형도전) RFP 설명회 및 네트워킹 데이 개최 안내</t>
+          <t>「2026년 구매연계ㆍ상생협력 R&amp;D사업 우수성과 유공」 포상 대상자 모집 공고</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6223,7 +6187,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -6253,7 +6217,7 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>https://www.tipa.or.kr/s040101/view/id/17458</t>
+          <t>https://www.tipa.or.kr/s040101/view/id/17600</t>
         </is>
       </c>
     </row>
@@ -6270,60 +6234,2675 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
+          <t>ETC</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>사업공고</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>2026년도 임무수요기반 성층권 드론 실증 플랫폼 개발 사업 2단계 신규과제 공고</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>우주항공청</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2026-08-03</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" t="inlineStr">
+        <is>
+          <t>마감</t>
+        </is>
+      </c>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=022957&amp;sorgnBsnsCd=S051446</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>조달청</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>입찰공고</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>2026학년도 남성초등학교 운반위탁급식(벌크식) 납품업체 선정 입찰</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>부산광역시교육청 부산광역시서부교육청 남성초등학교</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>하성준</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>마감</t>
+        </is>
+      </c>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01660843&amp;bidPbancOrd=000</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>조달청</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>입찰공고</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>2026년 문화체육관광 연구개발사업 성과조사 분석 및 사업평가 대응 위탁용역</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>한국콘텐츠진흥원</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>박종윤</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" t="inlineStr">
+        <is>
+          <t>마감</t>
+        </is>
+      </c>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01661573&amp;bidPbancOrd=000</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>조달청</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>입찰공고</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>2026 포항 해병대 문화축제 행사대행 용역</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>경상북도 포항시</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>고성철</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N88" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01661602&amp;bidPbancOrd=000</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>조달청</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>입찰공고</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>2026 국가유산 미디어아트 구 군산세관본관 등 물품임차 용역</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>전북특별자치도 군산시</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>양미진</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>마감</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01661619&amp;bidPbancOrd=000</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>조달청</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>입찰공고</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>2026년 이웃종교스테이 기획 및 행사운영 용역</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>한국종교인평화회의</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>마감</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01661461&amp;bidPbancOrd=000</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>조달청</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>입찰공고</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>2026년 제19회 김포 세계인 큰잔치 행사 대행 용역</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>김포시외국인주민지원센터</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>황유선</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>마감</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01661458&amp;bidPbancOrd=000</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>조달청</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>입찰공고</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>2026학년도 상봉중학교  2학년 수련활동 위탁용역 입찰공고(2단계입찰규격-가격분리 동시입찰)</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>서울특별시동부교육청 상봉중학교</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>장현우</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>마감</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01661465&amp;bidPbancOrd=000</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>조달청</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>입찰공고</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>2026학년도 선덕고등학교 1,2학년 소규모테마형 교육여행 위탁용역 업체 선정 전자입찰 공고(긴급)</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>서울특별시교육청 선덕고등학교</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>임현진</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr">
+        <is>
+          <t>마감</t>
+        </is>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01661472&amp;bidPbancOrd=000</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>조달청</t>
+        </is>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C94" s="3" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="D94" s="3" t="inlineStr">
+        <is>
+          <t>입찰공고</t>
+        </is>
+      </c>
+      <c r="E94" s="4" t="inlineStr">
+        <is>
+          <t>2026년 스마트생태공장 구축사업_컨설팅 용역</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="inlineStr">
+        <is>
+          <t>(주)삼정산업</t>
+        </is>
+      </c>
+      <c r="G94" s="3" t="inlineStr">
+        <is>
+          <t>박제현</t>
+        </is>
+      </c>
+      <c r="H94" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I94" s="3" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="K94" s="3" t="inlineStr">
+        <is>
+          <t>시스템구축·전환</t>
+        </is>
+      </c>
+      <c r="L94" s="3" t="inlineStr">
+        <is>
+          <t>NetFUNNEL</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr">
+        <is>
+          <t>구축</t>
+        </is>
+      </c>
+      <c r="N94" s="3" t="inlineStr">
+        <is>
+          <t>마감</t>
+        </is>
+      </c>
+      <c r="O94" s="3" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01661481&amp;bidPbancOrd=000</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>조달청</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>미분류</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>입찰공고</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>2026학년도 상봉중학교  2학년 수련활동 위탁용역 입찰공고(2단계입찰규격-가격분리 동시입찰)</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>서울특별시동부교육청 상봉중학교</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>장현우</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2026-08-01</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr">
+        <is>
+          <t>마감</t>
+        </is>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>https://www.g2b.go.kr/link/PNPE027_01/single/?bidPbancNo=R26BK01661465&amp;bidPbancOrd=001</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>IRIS</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
           <t>RND</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D96" t="inlineStr">
         <is>
           <t>사업공고</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>2026년 NCP 활동지원사업 신규과제 2차공모</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>과학기술정보통신부</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr">
+        <is>
+          <t>마감</t>
+        </is>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=023157&amp;sorgnBsnsCd=S049489</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>NIPA</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>입찰공고</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>[입찰공고] 2026년 평가위원 전문분야 분류체계 개편 방안 조사·분석 용역</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>https://www.nipa.kr/home/2-3/16881</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>NIPA</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>입찰공고</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>[입찰공고] 2026년 공공AX 프로젝트 사업 성과분석 용역</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>https://www.nipa.kr/home/2-3/16880</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>NIPA</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>입찰공고</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>[입찰공고] 2026년 부처협업 기반 AI확산 사업 성과분석 용역</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2026-07-29</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>https://www.nipa.kr/home/2-3/16879</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>TIPA</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>RND</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>지원사업공고</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>2026년 중소기업 R&amp;D 우수성과 50선 모집 연장 공고</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>중소벤처기업부</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2026-07-27</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>https://www.tipa.or.kr/s040101/view/id/17581</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>NIPA</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>입찰공고</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>[조달청 입찰공고] 2026년 클라우드 인식확산 용역</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>https://www.nipa.kr/home/2-3/16867</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>국가AI전략위원회</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>ETC</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>('26. 7. 22.) 지역·필수·공공의료 공백 해소 위한보건의료 AI 대전환</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>국가AI전략위원회</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>aikoreaadmin</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>https://www.aikorea.go.kr/web/board/brdDetail.do?menu_cd=000012&amp;num=812&amp;currentPage=1&amp;searchData=&amp;searchText=</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
+        <is>
+          <t>국가AI전략위원회</t>
+        </is>
+      </c>
+      <c r="B103" s="3" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C103" s="3" t="inlineStr">
+        <is>
+          <t>ETC</t>
+        </is>
+      </c>
+      <c r="D103" s="3" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="E103" s="4" t="inlineStr">
+        <is>
+          <t>('26. 7. 20.) 국가AI전략위, 「에이전틱 AI 시대 국가 AI 컴퓨팅 전략」 세미나 개최</t>
+        </is>
+      </c>
+      <c r="F103" s="3" t="inlineStr">
+        <is>
+          <t>국가AI전략위원회</t>
+        </is>
+      </c>
+      <c r="G103" s="3" t="inlineStr">
+        <is>
+          <t>aikoreaadmin</t>
+        </is>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="I103" s="3" t="inlineStr"/>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>상</t>
+        </is>
+      </c>
+      <c r="K103" s="3" t="inlineStr">
+        <is>
+          <t>시스템구축·전환</t>
+        </is>
+      </c>
+      <c r="L103" s="3" t="inlineStr">
+        <is>
+          <t>NetFUNNEL</t>
+        </is>
+      </c>
+      <c r="M103" s="3" t="inlineStr">
+        <is>
+          <t>구축</t>
+        </is>
+      </c>
+      <c r="N103" s="3" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O103" s="3" t="inlineStr">
+        <is>
+          <t>https://www.aikorea.go.kr/web/board/brdDetail.do?menu_cd=000012&amp;num=801&amp;currentPage=1&amp;searchData=&amp;searchText=</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>TIPA</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>RND</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>지원사업공고</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>제2회 제조AI 솔루션 공모전 공고</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>중소벤처기업부</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>https://www.tipa.or.kr/s040101/view/id/17570</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>NIPA</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>입찰공고</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>[입찰재공고] 2026 오픈소스 페스티벌 운영 용역</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>https://www.nipa.kr/home/2-3/16856</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>KIAT</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>RND</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>과제</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>2026년 첨단분야 인턴십 지원사업 3차 공고</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>산업통상부</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr">
+        <is>
+          <t>마감</t>
+        </is>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>https://k-pass.kr/notice/ancList.do</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>국가AI전략위원회</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>ETC</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="E107" s="2" t="inlineStr">
+        <is>
+          <t>('26. 7. 14.) 국가AI전략위, ‘AI 데이터센터 산업생태계 육성 간담회’ 개최</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>국가AI전략위원회</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>aikoreaadmin</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>https://www.aikorea.go.kr/web/board/brdDetail.do?menu_cd=000012&amp;num=791&amp;currentPage=1&amp;searchData=&amp;searchText=</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>국가AI전략위원회</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>ETC</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="E108" s="2" t="inlineStr">
+        <is>
+          <t>('26.7.20) Agentic AI 시대 국가 컴퓨팅 전략 세미나</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>국가AI전략위원회</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>aikorea</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>https://www.aikorea.go.kr/web/board/brdDetail.do?menu_cd=000010&amp;num=787&amp;currentPage=1&amp;searchData=&amp;searchText=</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>국가AI전략위원회</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>ETC</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="E109" s="2" t="inlineStr">
+        <is>
+          <t>('26. 7. 8.) 국가AI전략위, ‘AI 시대의 데이터 가치평가’ 세미나 개최</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>국가AI전략위원회</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>aikoreaadmin</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>https://www.aikorea.go.kr/web/board/brdDetail.do?menu_cd=000012&amp;num=782&amp;currentPage=1&amp;searchData=&amp;searchText=</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>IRIS</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>RND</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>사업공고</t>
+        </is>
+      </c>
+      <c r="E110" s="2" t="inlineStr">
+        <is>
+          <t>2026년도 국제공동연구 신속지원사업(미국 제네시스 미션과의 협력을 위한 탐색연구) 신규과제 공모</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>과학기술정보통신부</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2026-07-08</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N110" t="inlineStr">
+        <is>
+          <t>마감</t>
+        </is>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=023018&amp;sorgnBsnsCd=S050518</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>국가AI전략위원회</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>ETC</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="E111" s="2" t="inlineStr">
+        <is>
+          <t>('26. 7. 7.) 국가AI전략위, 피지컬 AI가 이끄는 자율주행 혁신 간담회 개최</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>국가AI전략위원회</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>aikoreaadmin</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>https://www.aikorea.go.kr/web/board/brdDetail.do?menu_cd=000012&amp;num=776&amp;currentPage=1&amp;searchData=&amp;searchText=</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>TIPA</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>RND</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>지원사업공고</t>
+        </is>
+      </c>
+      <c r="E112" s="2" t="inlineStr">
+        <is>
+          <t>「2026 스마트공장 지원사업 우수사례 컨소시엄 선정」 참가기업 모집 공고</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>중소벤처기업부</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N112" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>https://www.tipa.or.kr/s040101/view/id/17537</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>TIPA</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>RND</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>지원사업공고</t>
+        </is>
+      </c>
+      <c r="E113" s="2" t="inlineStr">
+        <is>
+          <t>2026년 중소기업 R&amp;D 우수성과 50선 모집 공고</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>중소벤처기업부</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>https://www.tipa.or.kr/s040101/view/id/17524</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>TIPA</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>ETC</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>지원사업공고</t>
+        </is>
+      </c>
+      <c r="E114" s="2" t="inlineStr">
+        <is>
+          <t>ICT융합 스마트공장 보급·확산사업 사업비 정산 제2기 스마트 제조혁신 지정회계기관 모집 공고</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>중소벤처기업부</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>https://www.tipa.or.kr/s040101/view/id/17511</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>TIPA</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>RND</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>지원사업공고</t>
+        </is>
+      </c>
+      <c r="E115" s="2" t="inlineStr">
+        <is>
+          <t>한-호주 글로벌 R&amp;D 협력 포럼 개최 안내</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>중소벤처기업부</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2026-06-19</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>https://www.tipa.or.kr/s040101/view/id/17492</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>국가AI전략위원회</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>ETC</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="E116" s="2" t="inlineStr">
+        <is>
+          <t>('26. 6. 18.) 국가AI전략위, ‘보안취약점 상시 신고조치제 제도화 논의’ 세미나 개최</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>국가AI전략위원회</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>aikoreaadmin</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>https://www.aikorea.go.kr/web/board/brdDetail.do?menu_cd=000012&amp;num=737&amp;currentPage=1&amp;searchData=&amp;searchText=</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>국가AI전략위원회</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>ETC</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="E117" s="2" t="inlineStr">
+        <is>
+          <t>('26. 6. 17.) 국가AI전략위, 인문사회 기반 AI 융합인재양성 방향 논의</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>국가AI전략위원회</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>aikoreaadmin</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>https://www.aikorea.go.kr/web/board/brdDetail.do?menu_cd=000012&amp;num=733&amp;currentPage=1&amp;searchData=&amp;searchText=</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>국가AI전략위원회</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>ETC</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="E118" s="2" t="inlineStr">
+        <is>
+          <t>('26.6.18.) 보안취약점 상시 신고조치제 제도화 관련 세미나</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>국가AI전략위원회</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>aikorea</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N118" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>https://www.aikorea.go.kr/web/board/brdDetail.do?menu_cd=000010&amp;num=731&amp;currentPage=1&amp;searchData=&amp;searchText=</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>국가AI전략위원회</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>ETC</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>공지사항</t>
+        </is>
+      </c>
+      <c r="E119" s="2" t="inlineStr">
+        <is>
+          <t>('26.6.17.) AI교육정책 포럼_인문사회 AX 교육은 왜 필요하며 어떻게 할 것인가?</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>국가AI전략위원회</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>aikorea</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2026-06-16</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N119" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>https://www.aikorea.go.kr/web/board/brdDetail.do?menu_cd=000010&amp;num=729&amp;currentPage=1&amp;searchData=&amp;searchText=</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>TIPA</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>RND</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>지원사업공고</t>
+        </is>
+      </c>
+      <c r="E120" s="2" t="inlineStr">
+        <is>
+          <t>2026년 창업성장기술개발(디딤돌) 소상공인R&amp;D 오디션 시민참여단 모집 안내</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>중소벤처기업부</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>https://www.tipa.or.kr/s040101/view/id/17459</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>TIPA</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>사업부</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>BID</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>지원사업공고</t>
+        </is>
+      </c>
+      <c r="E121" s="2" t="inlineStr">
+        <is>
+          <t>2026 민관공동기술사업화R&amp;D(구매연계 혁신형도전) RFP 설명회 및 네트워킹 데이 개최 안내</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>중소벤처기업부</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>진행중</t>
+        </is>
+      </c>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>https://www.tipa.or.kr/s040101/view/id/17458</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>IRIS</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>R&amp;D</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>RND</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>사업공고</t>
+        </is>
+      </c>
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>2026년도 범부처 현장수요 신속대응 연구개발(R&amp;D) KISA 전담 지정 과제</t>
         </is>
       </c>
-      <c r="F85" t="inlineStr">
+      <c r="F122" t="inlineStr">
         <is>
           <t>개인정보보호위원회</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H122" t="inlineStr">
         <is>
           <t>2026-04-16</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
+      <c r="I122" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>하</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>진행중</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>하</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>마감</t>
+        </is>
+      </c>
+      <c r="O122" t="inlineStr">
         <is>
           <t>https://www.iris.go.kr/contents/retrieveBsnsAncmView.do?ancmId=023477&amp;sorgnBsnsCd=S051638</t>
         </is>
@@ -6415,6 +8994,43 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E83" r:id="rId82"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E84" r:id="rId83"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E122" r:id="rId121"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
